--- a/Data/EXCEL/Transfer/salemon/202512/6699-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/6699-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C9E31FA-F420-4890-9C21-80119D8CDA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BF3ECDD-CADE-40DD-A3C6-C89D654CB8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{1CBAF550-E8C4-490E-810D-7340554A80D4}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{3F6E8D02-CC9E-47B4-99A3-B56365096A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="6699-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -1258,20 +1258,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0226F5D-8D51-4F55-8D8A-F4622434AE1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6807441C-7A03-488F-8209-57B6DAF2FDE1}">
   <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="7" width="11.25" customWidth="1"/>
-    <col min="8" max="9" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="11.75" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="11.75" customWidth="1"/>
-    <col min="13" max="14" width="13.5" customWidth="1"/>
-    <col min="15" max="15" width="11.75" customWidth="1"/>
-    <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="7" width="6.875" customWidth="1"/>
+    <col min="8" max="9" width="8.25" customWidth="1"/>
+    <col min="10" max="10" width="7.25" customWidth="1"/>
+    <col min="11" max="11" width="8.25" customWidth="1"/>
+    <col min="12" max="12" width="7.25" customWidth="1"/>
+    <col min="13" max="14" width="8.25" customWidth="1"/>
+    <col min="15" max="15" width="7.25" customWidth="1"/>
+    <col min="16" max="16" width="8.25" customWidth="1"/>
+    <col min="17" max="17" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
